--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_197_R20.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_197_R20.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.13</v>
+        <v>3.6224</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3674</v>
+        <v>2.927</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.6954</v>
       </c>
       <c r="G2" t="n">
         <v>1.399</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5017</v>
+        <v>-0.0059</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4437</v>
+        <v>-0.8841</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9454</v>
+        <v>0.8782</v>
       </c>
       <c r="V2" t="n">
         <v>0.1418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0921</v>
+        <v>1.7613</v>
       </c>
       <c r="E3" t="n">
-        <v>1.25</v>
+        <v>1.3561</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8421</v>
+        <v>0.4052</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9048</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6875</v>
+        <v>0.3567</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4832</v>
+        <v>-0.3771</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1707</v>
+        <v>0.7339</v>
       </c>
       <c r="V3" t="n">
         <v>3.4691</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.726</v>
+        <v>0.8103</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1612</v>
+        <v>1.2792</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4353</v>
+        <v>-0.4689</v>
       </c>
       <c r="G4" t="n">
         <v>0.8334</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.7912</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4189</v>
+        <v>-1.301</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5434</v>
+        <v>0.5098</v>
       </c>
       <c r="V4" t="n">
         <v>0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5674</v>
+        <v>0.6683</v>
       </c>
       <c r="E5" t="n">
         <v>-0.06419999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6317</v>
+        <v>0.7325</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0593</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4635</v>
+        <v>-0.3626</v>
       </c>
       <c r="T5" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V5" t="n">
         <v>0.3943</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.268</v>
+        <v>0.4606</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4113</v>
+        <v>-0.2187</v>
       </c>
       <c r="F6" t="n">
         <v>0.6793</v>
@@ -922,10 +922,10 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0747</v>
+        <v>0.118</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4481</v>
+        <v>-0.2555</v>
       </c>
       <c r="U6" t="n">
         <v>0.3734</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5362</v>
+        <v>-0.6535</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2158</v>
+        <v>-1.0979</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6796</v>
+        <v>0.4444</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2655</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0514</v>
+        <v>-0.0659</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6489</v>
+        <v>0.4136</v>
       </c>
       <c r="V7" t="n">
         <v>0.1418</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.391</v>
+        <v>-1.2901</v>
       </c>
       <c r="E8" t="n">
         <v>-0.1536</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2373</v>
+        <v>-1.1365</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1619</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1568</v>
+        <v>-0.056</v>
       </c>
       <c r="T8" t="n">
         <v>-0.224</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1197</v>
+        <v>-2.0525</v>
       </c>
       <c r="E9" t="n">
         <v>-3.033</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9133</v>
+        <v>0.9805</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5434</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3444</v>
+        <v>-0.2772</v>
       </c>
       <c r="T9" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1037</v>
+        <v>0.1709</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9186</v>
+        <v>-3.4257</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9029</v>
+        <v>-4.6788</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9843</v>
+        <v>1.2531</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2763</v>
@@ -1234,13 +1234,13 @@
         <v>2.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1062</v>
+        <v>-0.6133</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1554</v>
+        <v>-0.9313</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0492</v>
+        <v>0.3181</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2857</v>
+        <v>-6.0788</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8011</v>
+        <v>-5.695</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4846</v>
+        <v>-0.3838</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8099</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6049</v>
+        <v>-0.398</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8566</v>
+        <v>-0.7506</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2517</v>
+        <v>0.3525</v>
       </c>
       <c r="V11" t="n">
         <v>1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2976</v>
+        <v>-6.4674</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.0356</v>
+        <v>-5.3397</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2621</v>
+        <v>-1.1277</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7611</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6808999999999999</v>
+        <v>0.1494</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8215</v>
+        <v>-0.1256</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1406</v>
+        <v>0.275</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6083</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.7653</v>
+        <v>-12.6451</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.8389</v>
+        <v>-14.7186</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0736</v>
+        <v>2.0735</v>
       </c>
       <c r="G13" t="n">
         <v>-9.1349</v>
@@ -1468,13 +1468,13 @@
         <v>15.077</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.0663</v>
+        <v>-1.946</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.2704</v>
+        <v>-6.150200000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>4.2041</v>
+        <v>4.2042</v>
       </c>
       <c r="V13" t="n">
         <v>3.0748</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6898</v>
+        <v>8.1959</v>
       </c>
       <c r="E14" t="n">
-        <v>4.182</v>
+        <v>4.8897</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5078</v>
+        <v>3.3062</v>
       </c>
       <c r="G14" t="n">
         <v>5.6318</v>
@@ -1546,13 +1546,13 @@
         <v>3.2473</v>
       </c>
       <c r="S14" t="n">
-        <v>0.058</v>
+        <v>0.5641</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.643</v>
+        <v>-0.9353</v>
       </c>
       <c r="U14" t="n">
-        <v>1.701</v>
+        <v>1.4993</v>
       </c>
       <c r="V14" t="n">
         <v>1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3844</v>
+        <v>5.0743</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6159</v>
+        <v>3.9698</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7685</v>
+        <v>1.1046</v>
       </c>
       <c r="G15" t="n">
         <v>4.0778</v>
@@ -1624,13 +1624,13 @@
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8531</v>
+        <v>-0.1632</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8962</v>
+        <v>-0.5423</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0431</v>
+        <v>0.3791</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8306</v>
+        <v>2.9548</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7348</v>
+        <v>2.027</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0958</v>
+        <v>0.9278</v>
       </c>
       <c r="G16" t="n">
         <v>1.7546</v>
@@ -1702,13 +1702,13 @@
         <v>3.2473</v>
       </c>
       <c r="S16" t="n">
-        <v>0.973</v>
+        <v>0.0973</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0044</v>
+        <v>-0.7033</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9687</v>
+        <v>0.8006</v>
       </c>
       <c r="V16" t="n">
         <v>-2.1444</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5439</v>
+        <v>1.0886</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0111</v>
+        <v>-0.5786</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5328</v>
+        <v>1.6672</v>
       </c>
       <c r="G17" t="n">
         <v>1.3663</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2652</v>
+        <v>0.8098</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6765</v>
+        <v>0.0868</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5887</v>
+        <v>0.7231</v>
       </c>
       <c r="V17" t="n">
         <v>0.5361</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. NEBO</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2428</v>
+        <v>0.035</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2955</v>
+        <v>-2.8852</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5383</v>
+        <v>2.9202</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3662</v>
+        <v>-0.2732</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6371</v>
+        <v>-0.1861</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2709</v>
+        <v>-0.0871</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3519</v>
+        <v>-1.0023</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0943</v>
+        <v>-1.2331</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2576</v>
+        <v>0.2308</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0142</v>
+        <v>0.7292</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5427999999999999</v>
+        <v>1.047</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5286</v>
+        <v>-0.3178</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2013</v>
+        <v>-0.1041</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0148</v>
+        <v>-0.7231</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1866</v>
+        <v>0.619</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3969</v>
+        <v>-0.2836</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.1829</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.214</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2636</v>
+        <v>-0.0784</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5661</v>
+        <v>-1.4481</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3025</v>
+        <v>1.3697</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2261</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4112</v>
+        <v>-0.226</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2609</v>
+        <v>0.3282</v>
       </c>
       <c r="V19" t="n">
         <v>0.1418</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>J. NEBO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9073</v>
+        <v>-0.1555</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.357</v>
+        <v>-2.593</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4497</v>
+        <v>2.4375</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2732</v>
+        <v>2.3662</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1861</v>
+        <v>2.6371</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0871</v>
+        <v>-0.2709</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0023</v>
+        <v>2.3519</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2331</v>
+        <v>2.0943</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2308</v>
+        <v>0.2576</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7292</v>
+        <v>0.0142</v>
       </c>
       <c r="N20" t="n">
-        <v>1.047</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3178</v>
+        <v>-0.5286</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0464</v>
+        <v>0.803</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1949</v>
+        <v>-0.2827</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1485</v>
+        <v>1.0857</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2836</v>
+        <v>-2.3969</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-1.1829</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2836</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1165</v>
+        <v>-0.7284</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6148</v>
+        <v>-2.025</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4983</v>
+        <v>1.2967</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3421</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5298</v>
+        <v>0.9179</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8962</v>
+        <v>-0.3064</v>
       </c>
       <c r="U21" t="n">
-        <v>1.426</v>
+        <v>1.2243</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6387</v>
+        <v>-2.6209</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7839</v>
+        <v>-3.43</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1452</v>
+        <v>0.8091</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2203</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3497</v>
+        <v>0.3675</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.6111</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2206,13 +2206,13 @@
         <v>13.7654</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0735</v>
+        <v>-2.0734</v>
       </c>
       <c r="F23" t="n">
-        <v>15.8389</v>
+        <v>15.839</v>
       </c>
       <c r="G23" t="n">
-        <v>9.135</v>
+        <v>9.135000000000002</v>
       </c>
       <c r="H23" t="n">
         <v>10.7076</v>
@@ -2251,10 +2251,10 @@
         <v>3.0663</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.2042</v>
+        <v>-4.2041</v>
       </c>
       <c r="U23" t="n">
-        <v>7.2706</v>
+        <v>7.2704</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0748</v>
